--- a/customs_clearance.xlsx
+++ b/customs_clearance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C93A51-2B8A-4702-A20E-01EF1CFCF8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494098F5-56DA-4C05-B6E3-B7554E5BEB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A68FCA33-A009-496D-9E32-EA252D1F3209}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>company</t>
   </si>
@@ -54,13 +54,43 @@
   </si>
   <si>
     <t>base</t>
+  </si>
+  <si>
+    <t>Pronvattana Shipping</t>
+  </si>
+  <si>
+    <t>K. ปุ้ย</t>
+  </si>
+  <si>
+    <t>expshpg@pornvatana-transport.com</t>
+  </si>
+  <si>
+    <t>089-129-1813</t>
+  </si>
+  <si>
+    <t>PAT, LKB, LCB</t>
+  </si>
+  <si>
+    <t>Far Far Shipping Service (แม่สอด)</t>
+  </si>
+  <si>
+    <t>K.เจี๊ยบ</t>
+  </si>
+  <si>
+    <t>jeab_kaneing@hotmail.com</t>
+  </si>
+  <si>
+    <t>081-605-0456</t>
+  </si>
+  <si>
+    <t>Maesod , Yangon</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,6 +101,14 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -93,16 +131,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -435,8 +476,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1160DCEC-669B-4EE7-AA0F-8CA2B0588CAF}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -455,7 +502,45 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{26221D1D-DFEE-441F-84DE-79BE92C2D586}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{0F69C1EF-F701-4E07-B380-03816F6EEA7C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/customs_clearance.xlsx
+++ b/customs_clearance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494098F5-56DA-4C05-B6E3-B7554E5BEB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD508665-5AB5-4465-8C2B-118F61006341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A68FCA33-A009-496D-9E32-EA252D1F3209}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
   <si>
     <t>company</t>
   </si>
@@ -84,6 +84,162 @@
   </si>
   <si>
     <t>Maesod , Yangon</t>
+  </si>
+  <si>
+    <t>Maesod shipping service lp. (แม่สอด)</t>
+  </si>
+  <si>
+    <t>K. แตงโม</t>
+  </si>
+  <si>
+    <t>Shipping @ Maesod for Myanmar</t>
+  </si>
+  <si>
+    <t>maesodshipping@hotmail.co.th</t>
+  </si>
+  <si>
+    <t>T.S.P Shipping Service</t>
+  </si>
+  <si>
+    <t>K ปุ้ม</t>
+  </si>
+  <si>
+    <t>FTS Transport Service</t>
+  </si>
+  <si>
+    <t>K. Pongthep</t>
+  </si>
+  <si>
+    <t>BEST LOGISTICS &amp; SERVICES</t>
+  </si>
+  <si>
+    <t>K.เก่ง(ติดต่องาน)</t>
+  </si>
+  <si>
+    <t>ONE PLUS ONE LOGISTICS</t>
+  </si>
+  <si>
+    <t>K.หนิง</t>
+  </si>
+  <si>
+    <t>Amazing Logistics and Supply Chain</t>
+  </si>
+  <si>
+    <t>K. Wisert</t>
+  </si>
+  <si>
+    <t>Prasit Enterprise &amp; Freight Co., Ltd.</t>
+  </si>
+  <si>
+    <t>K. ณัฐพงศ์(ติดต่องาน)</t>
+  </si>
+  <si>
+    <t>EXIM Agency Co., Ltd.</t>
+  </si>
+  <si>
+    <t>K. Jing (ขาเข้า)</t>
+  </si>
+  <si>
+    <t>K. Lhin (ขาออก)</t>
+  </si>
+  <si>
+    <t>X Logistics</t>
+  </si>
+  <si>
+    <t>K. บี</t>
+  </si>
+  <si>
+    <t>Bevery Group</t>
+  </si>
+  <si>
+    <t>K. เชิด</t>
+  </si>
+  <si>
+    <t>G&amp;T Shipping</t>
+  </si>
+  <si>
+    <t>K. ต้อม</t>
+  </si>
+  <si>
+    <t>spongky_tom@hotmail.com</t>
+  </si>
+  <si>
+    <t>aslann@beverygroup.com</t>
+  </si>
+  <si>
+    <t>kamoltip.k@3xlogistics.com</t>
+  </si>
+  <si>
+    <t>export01@exim-thai.com</t>
+  </si>
+  <si>
+    <t>import01@exim-thai.com</t>
+  </si>
+  <si>
+    <t>pefshipping.dept@gmail.com</t>
+  </si>
+  <si>
+    <t>wisert@amazing-lsc.com</t>
+  </si>
+  <si>
+    <t>import4-cs@bestlogistics.co.th</t>
+  </si>
+  <si>
+    <t>pongthep@fts.co.th</t>
+  </si>
+  <si>
+    <t>tspshipping@gmail.com</t>
+  </si>
+  <si>
+    <t>watcharee@oneplusone-logist.com</t>
+  </si>
+  <si>
+    <t>081-8473461</t>
+  </si>
+  <si>
+    <t>081-846-6951</t>
+  </si>
+  <si>
+    <t>089-896-3949</t>
+  </si>
+  <si>
+    <t>086-319-9226</t>
+  </si>
+  <si>
+    <t>089-210-2727</t>
+  </si>
+  <si>
+    <t>061-941-4649</t>
+  </si>
+  <si>
+    <t>084-161-1306</t>
+  </si>
+  <si>
+    <t>088-0223392</t>
+  </si>
+  <si>
+    <t>088-0223389</t>
+  </si>
+  <si>
+    <t>098-272-8116, 02-738-4324</t>
+  </si>
+  <si>
+    <t>089-920-6112</t>
+  </si>
+  <si>
+    <t>090-902-2380</t>
+  </si>
+  <si>
+    <t>PAT, LKB</t>
+  </si>
+  <si>
+    <t>LCB</t>
+  </si>
+  <si>
+    <t>สุวรรณภูมิ</t>
+  </si>
+  <si>
+    <t>PAT,LKB</t>
   </si>
 </sst>
 </file>
@@ -135,12 +291,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -476,13 +635,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1160DCEC-669B-4EE7-AA0F-8CA2B0588CAF}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -536,10 +696,226 @@
         <v>14</v>
       </c>
     </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="E11:E12"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{26221D1D-DFEE-441F-84DE-79BE92C2D586}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{0F69C1EF-F701-4E07-B380-03816F6EEA7C}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{850169D8-C590-46C4-AC73-5B705FE0DD05}"/>
+    <hyperlink ref="C15" r:id="rId4" xr:uid="{14B282E9-F4D7-40C4-820D-69CDF2071C01}"/>
+    <hyperlink ref="C14" r:id="rId5" xr:uid="{6C83B108-76D8-499C-957E-A0D42A9CB591}"/>
+    <hyperlink ref="C13" r:id="rId6" xr:uid="{931B9E41-156C-47A5-8C7C-3CE7EF919D44}"/>
+    <hyperlink ref="C12" r:id="rId7" xr:uid="{078C0FC5-B0CE-49FE-8336-8D495D8BC7FD}"/>
+    <hyperlink ref="C11" r:id="rId8" xr:uid="{81C624EE-D1C0-430D-A63C-33AAD6582C74}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{1F17D72E-3C36-41EB-B950-B8D747A8220C}"/>
+    <hyperlink ref="C9" r:id="rId10" xr:uid="{E051D919-BE5B-4956-B522-322EA3FB2AFF}"/>
+    <hyperlink ref="C7" r:id="rId11" xr:uid="{03AD864A-F4A0-4A9E-A1AE-AA7A79384945}"/>
+    <hyperlink ref="C6" r:id="rId12" xr:uid="{A8B1FAEA-FFEC-4DF9-8935-8C367E4FDD08}"/>
+    <hyperlink ref="C5" r:id="rId13" xr:uid="{5BEEE1CD-A53B-4BB4-890A-B4AD2EF59625}"/>
+    <hyperlink ref="C8" r:id="rId14" xr:uid="{93276671-12CD-422A-A919-ADDFAE0867A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/customs_clearance.xlsx
+++ b/customs_clearance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD508665-5AB5-4465-8C2B-118F61006341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878CE669-C83C-4EB4-8018-C9084AA24B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A68FCA33-A009-496D-9E32-EA252D1F3209}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
   <si>
     <t>company</t>
   </si>
@@ -298,7 +298,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -833,7 +833,9 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
@@ -843,7 +845,9 @@
       <c r="D12" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -897,10 +901,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="E11:E12"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{26221D1D-DFEE-441F-84DE-79BE92C2D586}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{0F69C1EF-F701-4E07-B380-03816F6EEA7C}"/>
